--- a/data/trans_camb/P1427-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1427-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,35</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,83</t>
+          <t>-2,4; 0,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,77</t>
+          <t>-0,68; 2,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,46</t>
+          <t>-0,0; 3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,84</t>
+          <t>0,46; 2,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,66</t>
+          <t>-0,85; 1,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,36</t>
+          <t>0,01; 2,33</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>519,37%</t>
+          <t>542,29%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>147,86%</t>
+          <t>144,73%</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-92,18; 211,68</t>
+          <t>-93,76; 307,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 470,89</t>
+          <t>-34,23; 593,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 378,23</t>
+          <t>-66,62; 394,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 560,49</t>
+          <t>-8,35; 537,54</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,89</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,67</t>
+          <t>-2,82; 0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,14</t>
+          <t>-1,73; 2,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 1,22</t>
+          <t>-2,74; 1,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,68</t>
+          <t>-1,05; 2,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,49</t>
+          <t>-1,84; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,06</t>
+          <t>-0,5; 2,02</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103,99%</t>
+          <t>115,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>66,05%</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 196,31</t>
+          <t>-100,0; 206,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 333,34</t>
+          <t>-60,12; 347,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,59; —</t>
+          <t>-54,24; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,56; 107,16</t>
+          <t>-83,25; 101,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,96; 319,7</t>
+          <t>-28,07; 329,82</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>1,38</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,56</t>
+          <t>-1,99; 1,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,22</t>
+          <t>-1,43; 1,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,39</t>
+          <t>-0,95; 4,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,37</t>
+          <t>1,79; 7,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,67</t>
+          <t>-1,09; 1,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,12</t>
+          <t>-0,06; 2,84</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-24,95%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367,14%</t>
+          <t>357,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,49; 105,31</t>
+          <t>-62,63; 84,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,21; 65,42</t>
+          <t>-45,29; 123,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,41; 1892,26</t>
+          <t>31,33; 1668,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 120,14</t>
+          <t>-43,64; 138,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,8; 131,18</t>
+          <t>-5,72; 198,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>1,07</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -1,1</t>
+          <t>-3,4; -1,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,78</t>
+          <t>-0,47; 2,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,9</t>
+          <t>-0,81; 2,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,94</t>
+          <t>-0,2; 2,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; -0,15</t>
+          <t>-1,99; -0,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,95</t>
+          <t>0,02; 2,11</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-90,32; -45,65</t>
+          <t>-90,51; -51,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 137,05</t>
+          <t>-14,17; 107,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 221,75</t>
+          <t>-40,53; 230,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 198,36</t>
+          <t>-11,04; 291,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,26; -8,1</t>
+          <t>-67,86; -6,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 107,51</t>
+          <t>0,1; 114,85</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,81</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,45</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,46</t>
+          <t>-1,2; 1,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,93</t>
+          <t>1,3; 4,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,36</t>
+          <t>-2,35; 1,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,57</t>
+          <t>2,0; 5,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,96</t>
+          <t>-1,5; 0,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,5</t>
+          <t>1,99; 4,76</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>265,16%</t>
+          <t>213,94%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109,25%</t>
+          <t>109,64%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>146,7%</t>
+          <t>132,36%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,08; 203,32</t>
+          <t>-56,21; 251,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>54,52; 804,26</t>
+          <t>39,92; 653,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,5; 55,83</t>
+          <t>-53,63; 65,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25,32; 258,21</t>
+          <t>42,27; 225,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,64; 51,19</t>
+          <t>-46,35; 46,01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,64; 281,87</t>
+          <t>53,38; 254,54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,57</t>
+          <t>0,2; 2,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,62; -0,33</t>
+          <t>-3,54; -0,31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,01</t>
+          <t>-0,61; 3,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,15</t>
+          <t>-2,84; -0,22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,44</t>
+          <t>-0,47; 2,45</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-65,88; -6,77</t>
+          <t>-65,96; -5,76</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 89,24</t>
+          <t>-13,19; 87,22</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-64,48; -2,57</t>
+          <t>-65,75; -7,94</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 90,9</t>
+          <t>-12,17; 84,53</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; -0,29</t>
+          <t>-1,59; -0,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,85</t>
+          <t>0,4; 1,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,39</t>
+          <t>-1,21; 0,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,49</t>
+          <t>0,95; 2,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; -0,25</t>
+          <t>-1,15; -0,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,95</t>
+          <t>0,9; 1,92</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-64,89; -18,16</t>
+          <t>-65,62; -18,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,03; 113,23</t>
+          <t>16,46; 114,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 18,11</t>
+          <t>-39,38; 19,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19,7; 110,02</t>
+          <t>30,24; 109,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-44,48; -10,54</t>
+          <t>-44,33; -8,3</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,3; 94,82</t>
+          <t>34,0; 91,82</t>
         </is>
       </c>
     </row>
